--- a/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - EOSB and Leave Provisions 2026-09.xlsx
+++ b/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - EOSB and Leave Provisions 2026-09.xlsx
@@ -460,7 +460,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5B4636"/>
+        <fgColor rgb="FF321E1E"/>
       </patternFill>
     </fill>
   </fills>

--- a/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - EOSB and Leave Provisions 2026-09.xlsx
+++ b/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - EOSB and Leave Provisions 2026-09.xlsx
@@ -73,352 +73,352 @@
     <t>SDH-1006</t>
   </si>
   <si>
+    <t>Saad Al Shammari</t>
+  </si>
+  <si>
+    <t>SDH-1007</t>
+  </si>
+  <si>
+    <t>Nasser Al Qahtani</t>
+  </si>
+  <si>
+    <t>SDH-1008</t>
+  </si>
+  <si>
+    <t>Anas Al Qurashi</t>
+  </si>
+  <si>
+    <t>SDH-1009</t>
+  </si>
+  <si>
+    <t>Osama Al Tamimi</t>
+  </si>
+  <si>
+    <t>SDH-1010</t>
+  </si>
+  <si>
+    <t>Amal Al Yami</t>
+  </si>
+  <si>
+    <t>SDH-1011</t>
+  </si>
+  <si>
+    <t>Vikram Chowdhury</t>
+  </si>
+  <si>
+    <t>SDH-1012</t>
+  </si>
+  <si>
+    <t>Fahad Al Anazi</t>
+  </si>
+  <si>
+    <t>SDH-1013</t>
+  </si>
+  <si>
+    <t>Khalid Al Juhani</t>
+  </si>
+  <si>
+    <t>SDH-1014</t>
+  </si>
+  <si>
+    <t>Abdulaziz Al Tamimi</t>
+  </si>
+  <si>
+    <t>SDH-1015</t>
+  </si>
+  <si>
+    <t>Nikhil Menon</t>
+  </si>
+  <si>
+    <t>SDH-1016</t>
+  </si>
+  <si>
+    <t>Noura Al Subaie</t>
+  </si>
+  <si>
+    <t>SDH-1017</t>
+  </si>
+  <si>
+    <t>Hamad Al Sudairi</t>
+  </si>
+  <si>
+    <t>SDH-1018</t>
+  </si>
+  <si>
+    <t>Badr Al Fahad</t>
+  </si>
+  <si>
+    <t>SDH-1019</t>
+  </si>
+  <si>
+    <t>Sami Shawky</t>
+  </si>
+  <si>
+    <t>SDH-1020</t>
+  </si>
+  <si>
+    <t>Haifa Al Asmari</t>
+  </si>
+  <si>
+    <t>SDH-1021</t>
+  </si>
+  <si>
+    <t>Mohammed Al Shehri</t>
+  </si>
+  <si>
+    <t>SDH-1022</t>
+  </si>
+  <si>
+    <t>Saad Al Subaie</t>
+  </si>
+  <si>
+    <t>SDH-1023</t>
+  </si>
+  <si>
+    <t>Ziyad Al Shammari</t>
+  </si>
+  <si>
+    <t>SDH-1024</t>
+  </si>
+  <si>
+    <t>Vikram DSouza</t>
+  </si>
+  <si>
+    <t>SDH-1025</t>
+  </si>
+  <si>
+    <t>Abdulrahman Al Asmari</t>
+  </si>
+  <si>
+    <t>SDH-1026</t>
+  </si>
+  <si>
+    <t>Faisal Al Mutairi</t>
+  </si>
+  <si>
+    <t>SDH-1027</t>
+  </si>
+  <si>
+    <t>Jose Santos</t>
+  </si>
+  <si>
+    <t>SDH-1028</t>
+  </si>
+  <si>
+    <t>Khalid Al Subaie</t>
+  </si>
+  <si>
+    <t>SDH-1029</t>
+  </si>
+  <si>
+    <t>Saad Al Saud</t>
+  </si>
+  <si>
+    <t>SDH-1030</t>
+  </si>
+  <si>
+    <t>Lulwa Al Rasheed</t>
+  </si>
+  <si>
+    <t>SDH-1031</t>
+  </si>
+  <si>
+    <t>Mansour Al Sudairi</t>
+  </si>
+  <si>
+    <t>SDH-1032</t>
+  </si>
+  <si>
+    <t>Badr Al Sheikh</t>
+  </si>
+  <si>
+    <t>SDH-1033</t>
+  </si>
+  <si>
+    <t>Sara Al Otaibi</t>
+  </si>
+  <si>
+    <t>SDH-1034</t>
+  </si>
+  <si>
+    <t>Haifa Al Qurashi</t>
+  </si>
+  <si>
+    <t>SDH-1035</t>
+  </si>
+  <si>
+    <t>Mostafa Gemayel</t>
+  </si>
+  <si>
+    <t>SDH-1036</t>
+  </si>
+  <si>
+    <t>Anas Al Malki</t>
+  </si>
+  <si>
+    <t>SDH-1037</t>
+  </si>
+  <si>
+    <t>Walid Haddad</t>
+  </si>
+  <si>
+    <t>SDH-1038</t>
+  </si>
+  <si>
+    <t>Priya Hossain</t>
+  </si>
+  <si>
+    <t>SDH-1039</t>
+  </si>
+  <si>
+    <t>Deema Al Subaie</t>
+  </si>
+  <si>
+    <t>SDH-1040</t>
+  </si>
+  <si>
+    <t>Badr Al Anazi</t>
+  </si>
+  <si>
+    <t>SDH-1041</t>
+  </si>
+  <si>
+    <t>Abeer Al Juhani</t>
+  </si>
+  <si>
+    <t>Yazeed Al Shammari</t>
+  </si>
+  <si>
+    <t>SDH-1043</t>
+  </si>
+  <si>
+    <t>Bandar Al Rashidi</t>
+  </si>
+  <si>
+    <t>SDH-1044</t>
+  </si>
+  <si>
+    <t>Angela Cruz</t>
+  </si>
+  <si>
+    <t>SDH-1045</t>
+  </si>
+  <si>
+    <t>Nasser Al Muqbel</t>
+  </si>
+  <si>
+    <t>SDH-1046</t>
+  </si>
+  <si>
+    <t>Anas Al Otaibi</t>
+  </si>
+  <si>
+    <t>SDH-1047</t>
+  </si>
+  <si>
+    <t>Hessa Al Subaie</t>
+  </si>
+  <si>
+    <t>SDH-1048</t>
+  </si>
+  <si>
+    <t>Hamad Al Saud</t>
+  </si>
+  <si>
+    <t>SDH-1049</t>
+  </si>
+  <si>
+    <t>Angela Santos</t>
+  </si>
+  <si>
+    <t>SDH-1050</t>
+  </si>
+  <si>
+    <t>Nawaf Al Ghamdi</t>
+  </si>
+  <si>
+    <t>SDH-1051</t>
+  </si>
+  <si>
     <t>Mishari Al Rasheed</t>
   </si>
   <si>
-    <t>SDH-1007</t>
-  </si>
-  <si>
-    <t>Saad Al Shammari</t>
-  </si>
-  <si>
-    <t>SDH-1008</t>
-  </si>
-  <si>
-    <t>Nasser Al Qahtani</t>
-  </si>
-  <si>
-    <t>SDH-1009</t>
-  </si>
-  <si>
-    <t>Anas Al Qurashi</t>
-  </si>
-  <si>
-    <t>SDH-1010</t>
-  </si>
-  <si>
-    <t>Osama Al Tamimi</t>
-  </si>
-  <si>
-    <t>SDH-1011</t>
-  </si>
-  <si>
-    <t>Amal Al Yami</t>
-  </si>
-  <si>
-    <t>SDH-1012</t>
-  </si>
-  <si>
-    <t>Vikram Chowdhury</t>
-  </si>
-  <si>
-    <t>SDH-1013</t>
-  </si>
-  <si>
-    <t>Fahad Al Anazi</t>
-  </si>
-  <si>
-    <t>SDH-1014</t>
-  </si>
-  <si>
-    <t>Khalid Al Juhani</t>
-  </si>
-  <si>
-    <t>SDH-1015</t>
-  </si>
-  <si>
-    <t>Abdulaziz Al Tamimi</t>
-  </si>
-  <si>
-    <t>SDH-1016</t>
-  </si>
-  <si>
-    <t>Nikhil Menon</t>
-  </si>
-  <si>
-    <t>SDH-1017</t>
-  </si>
-  <si>
-    <t>Noura Al Subaie</t>
-  </si>
-  <si>
-    <t>SDH-1018</t>
-  </si>
-  <si>
-    <t>Hamad Al Sudairi</t>
-  </si>
-  <si>
-    <t>SDH-1019</t>
-  </si>
-  <si>
-    <t>Badr Al Fahad</t>
-  </si>
-  <si>
-    <t>SDH-1020</t>
-  </si>
-  <si>
-    <t>Sami Shawky</t>
-  </si>
-  <si>
-    <t>SDH-1021</t>
-  </si>
-  <si>
-    <t>Haifa Al Asmari</t>
-  </si>
-  <si>
-    <t>SDH-1022</t>
-  </si>
-  <si>
-    <t>Mohammed Al Shehri</t>
-  </si>
-  <si>
-    <t>SDH-1023</t>
-  </si>
-  <si>
-    <t>Saad Al Subaie</t>
-  </si>
-  <si>
-    <t>SDH-1024</t>
-  </si>
-  <si>
-    <t>Ziyad Al Shammari</t>
-  </si>
-  <si>
-    <t>SDH-1025</t>
-  </si>
-  <si>
-    <t>Vikram DSouza</t>
-  </si>
-  <si>
-    <t>Abdulrahman Al Asmari</t>
-  </si>
-  <si>
-    <t>SDH-1027</t>
-  </si>
-  <si>
-    <t>Faisal Al Mutairi</t>
-  </si>
-  <si>
-    <t>SDH-1028</t>
-  </si>
-  <si>
-    <t>Jose Santos</t>
-  </si>
-  <si>
-    <t>SDH-1029</t>
-  </si>
-  <si>
-    <t>Khalid Al Subaie</t>
-  </si>
-  <si>
-    <t>SDH-1030</t>
-  </si>
-  <si>
-    <t>Saad Al Saud</t>
-  </si>
-  <si>
-    <t>SDH-1031</t>
-  </si>
-  <si>
-    <t>Lulwa Al Rasheed</t>
-  </si>
-  <si>
-    <t>SDH-1032</t>
-  </si>
-  <si>
-    <t>Mansour Al Sudairi</t>
-  </si>
-  <si>
-    <t>SDH-1033</t>
-  </si>
-  <si>
-    <t>Badr Al Sheikh</t>
-  </si>
-  <si>
-    <t>SDH-1034</t>
-  </si>
-  <si>
-    <t>Sara Al Otaibi</t>
-  </si>
-  <si>
-    <t>SDH-1035</t>
-  </si>
-  <si>
-    <t>Haifa Al Qurashi</t>
-  </si>
-  <si>
-    <t>SDH-1036</t>
-  </si>
-  <si>
-    <t>Mostafa Gemayel</t>
-  </si>
-  <si>
-    <t>SDH-1037</t>
-  </si>
-  <si>
-    <t>Anas Al Malki</t>
-  </si>
-  <si>
-    <t>SDH-1038</t>
-  </si>
-  <si>
-    <t>Walid Haddad</t>
-  </si>
-  <si>
-    <t>SDH-1039</t>
-  </si>
-  <si>
-    <t>Priya Hossain</t>
-  </si>
-  <si>
-    <t>SDH-1040</t>
-  </si>
-  <si>
-    <t>Deema Al Subaie</t>
-  </si>
-  <si>
-    <t>SDH-1041</t>
-  </si>
-  <si>
-    <t>Badr Al Anazi</t>
-  </si>
-  <si>
-    <t>SDH-1042</t>
-  </si>
-  <si>
-    <t>Abeer Al Juhani</t>
-  </si>
-  <si>
-    <t>SDH-1043</t>
-  </si>
-  <si>
-    <t>Yazeed Al Shammari</t>
-  </si>
-  <si>
-    <t>SDH-1044</t>
-  </si>
-  <si>
-    <t>Bandar Al Rashidi</t>
-  </si>
-  <si>
-    <t>SDH-1045</t>
-  </si>
-  <si>
-    <t>Angela Cruz</t>
-  </si>
-  <si>
-    <t>SDH-1046</t>
-  </si>
-  <si>
-    <t>Anas Al Otaibi</t>
-  </si>
-  <si>
-    <t>SDH-1047</t>
-  </si>
-  <si>
-    <t>Hessa Al Subaie</t>
-  </si>
-  <si>
-    <t>SDH-1048</t>
-  </si>
-  <si>
-    <t>Hamad Al Saud</t>
-  </si>
-  <si>
-    <t>SDH-1049</t>
-  </si>
-  <si>
-    <t>Angela Santos</t>
-  </si>
-  <si>
-    <t>SDH-1050</t>
-  </si>
-  <si>
-    <t>Nawaf Al Ghamdi</t>
-  </si>
-  <si>
-    <t>SDH-1051</t>
+    <t>SDH-1052</t>
+  </si>
+  <si>
+    <t>Tarek Abdelaziz</t>
+  </si>
+  <si>
+    <t>SDH-1053</t>
+  </si>
+  <si>
+    <t>Waleed Al Harbi</t>
+  </si>
+  <si>
+    <t>SDH-1054</t>
+  </si>
+  <si>
+    <t>Hani Masri</t>
+  </si>
+  <si>
+    <t>SDH-1055</t>
+  </si>
+  <si>
+    <t>Nasser Al Zahrani</t>
+  </si>
+  <si>
+    <t>SDH-1056</t>
+  </si>
+  <si>
+    <t>Grace Bautista</t>
+  </si>
+  <si>
+    <t>SDH-1057</t>
+  </si>
+  <si>
+    <t>Fahad Al Saud</t>
+  </si>
+  <si>
+    <t>SDH-1058</t>
+  </si>
+  <si>
+    <t>Anas Al Muqbel</t>
+  </si>
+  <si>
+    <t>SDH-1059</t>
+  </si>
+  <si>
+    <t>Ibrahim Al Mutairi</t>
+  </si>
+  <si>
+    <t>SDH-1060</t>
+  </si>
+  <si>
+    <t>Neha Siddiqui</t>
+  </si>
+  <si>
+    <t>SDH-1061</t>
+  </si>
+  <si>
+    <t>Rakan Al Nasser</t>
+  </si>
+  <si>
+    <t>SDH-1062</t>
+  </si>
+  <si>
+    <t>Munira Al Yami</t>
+  </si>
+  <si>
+    <t>SDH-1063</t>
+  </si>
+  <si>
+    <t>Munira Al Asmari</t>
+  </si>
+  <si>
+    <t>SDH-1064</t>
   </si>
   <si>
     <t>Ghadah Al Otaibi</t>
-  </si>
-  <si>
-    <t>SDH-1052</t>
-  </si>
-  <si>
-    <t>Tarek Abdelaziz</t>
-  </si>
-  <si>
-    <t>SDH-1053</t>
-  </si>
-  <si>
-    <t>Waleed Al Harbi</t>
-  </si>
-  <si>
-    <t>SDH-1054</t>
-  </si>
-  <si>
-    <t>Hani Masri</t>
-  </si>
-  <si>
-    <t>SDH-1055</t>
-  </si>
-  <si>
-    <t>Nasser Al Zahrani</t>
-  </si>
-  <si>
-    <t>SDH-1056</t>
-  </si>
-  <si>
-    <t>Grace Bautista</t>
-  </si>
-  <si>
-    <t>SDH-1057</t>
-  </si>
-  <si>
-    <t>Fahad Al Saud</t>
-  </si>
-  <si>
-    <t>SDH-1058</t>
-  </si>
-  <si>
-    <t>Anas Al Muqbel</t>
-  </si>
-  <si>
-    <t>SDH-1059</t>
-  </si>
-  <si>
-    <t>Ibrahim Al Mutairi</t>
-  </si>
-  <si>
-    <t>SDH-1060</t>
-  </si>
-  <si>
-    <t>Neha Siddiqui</t>
-  </si>
-  <si>
-    <t>SDH-1061</t>
-  </si>
-  <si>
-    <t>Rakan Al Nasser</t>
-  </si>
-  <si>
-    <t>SDH-1062</t>
-  </si>
-  <si>
-    <t>Munira Al Yami</t>
-  </si>
-  <si>
-    <t>SDH-1063</t>
-  </si>
-  <si>
-    <t>Munira Al Asmari</t>
-  </si>
-  <si>
-    <t>SDH-1064</t>
-  </si>
-  <si>
-    <t>Nasser Al Muqbel</t>
   </si>
   <si>
     <t>Total</t>
@@ -894,13 +894,13 @@
         <v>95825.59</v>
       </c>
       <c r="G2" s="4">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="H2" s="2">
         <v>1197</v>
       </c>
       <c r="I2" s="2">
-        <v>8977.5</v>
+        <v>5386.5</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -923,13 +923,13 @@
         <v>96070.47</v>
       </c>
       <c r="G3" s="4">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="H3" s="2">
         <v>1203.77</v>
       </c>
       <c r="I3" s="2">
-        <v>22269.68</v>
+        <v>16250.85</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -952,13 +952,13 @@
         <v>48924.95</v>
       </c>
       <c r="G4" s="4">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="H4" s="2">
         <v>618.77</v>
       </c>
       <c r="I4" s="2">
-        <v>8972.12</v>
+        <v>11447.18</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -981,13 +981,13 @@
         <v>54591.78</v>
       </c>
       <c r="G5" s="4">
-        <v>22.5</v>
+        <v>15.5</v>
       </c>
       <c r="H5" s="2">
         <v>720</v>
       </c>
       <c r="I5" s="2">
-        <v>16200</v>
+        <v>11160</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1010,13 +1010,13 @@
         <v>100228.44</v>
       </c>
       <c r="G6" s="4">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="H6" s="2">
         <v>1332</v>
       </c>
       <c r="I6" s="2">
-        <v>13986</v>
+        <v>21978</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1027,25 +1027,25 @@
         <v>20</v>
       </c>
       <c r="C7" s="1">
-        <v>44489</v>
+        <v>44495</v>
       </c>
       <c r="D7" s="2">
-        <v>21195</v>
+        <v>17685</v>
       </c>
       <c r="E7" s="3">
-        <v>4.951</v>
+        <v>4.934</v>
       </c>
       <c r="F7" s="2">
-        <v>52464.88</v>
+        <v>43631.08</v>
       </c>
       <c r="G7" s="4">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="H7" s="2">
-        <v>706.5</v>
+        <v>589.5</v>
       </c>
       <c r="I7" s="2">
-        <v>3885.75</v>
+        <v>7958.25</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1056,25 +1056,25 @@
         <v>22</v>
       </c>
       <c r="C8" s="1">
-        <v>44495</v>
+        <v>44498</v>
       </c>
       <c r="D8" s="2">
-        <v>17685</v>
+        <v>21060</v>
       </c>
       <c r="E8" s="3">
-        <v>4.934</v>
+        <v>4.926</v>
       </c>
       <c r="F8" s="2">
-        <v>43631.08</v>
+        <v>51871.07</v>
       </c>
       <c r="G8" s="4">
-        <v>10.5</v>
+        <v>23.5</v>
       </c>
       <c r="H8" s="2">
-        <v>589.5</v>
+        <v>702</v>
       </c>
       <c r="I8" s="2">
-        <v>6189.75</v>
+        <v>16497</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1085,25 +1085,25 @@
         <v>24</v>
       </c>
       <c r="C9" s="1">
-        <v>44498</v>
+        <v>44540</v>
       </c>
       <c r="D9" s="2">
-        <v>21060</v>
+        <v>13028</v>
       </c>
       <c r="E9" s="3">
-        <v>4.926</v>
+        <v>4.811</v>
       </c>
       <c r="F9" s="2">
-        <v>51871.07</v>
+        <v>31338.59</v>
       </c>
       <c r="G9" s="4">
-        <v>17.5</v>
+        <v>16.75</v>
       </c>
       <c r="H9" s="2">
-        <v>702</v>
+        <v>434.27</v>
       </c>
       <c r="I9" s="2">
-        <v>12285</v>
+        <v>7273.97</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1114,25 +1114,25 @@
         <v>26</v>
       </c>
       <c r="C10" s="1">
-        <v>44540</v>
+        <v>44584</v>
       </c>
       <c r="D10" s="2">
-        <v>13028</v>
+        <v>46103</v>
       </c>
       <c r="E10" s="3">
-        <v>4.811</v>
+        <v>4.69</v>
       </c>
       <c r="F10" s="2">
-        <v>31338.59</v>
+        <v>108121.01</v>
       </c>
       <c r="G10" s="4">
-        <v>12.75</v>
+        <v>3.75</v>
       </c>
       <c r="H10" s="2">
-        <v>434.27</v>
+        <v>1536.77</v>
       </c>
       <c r="I10" s="2">
-        <v>5536.9</v>
+        <v>5762.88</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1143,25 +1143,25 @@
         <v>28</v>
       </c>
       <c r="C11" s="1">
-        <v>44584</v>
+        <v>44585</v>
       </c>
       <c r="D11" s="2">
-        <v>46103</v>
+        <v>24638</v>
       </c>
       <c r="E11" s="3">
-        <v>4.69</v>
+        <v>4.688</v>
       </c>
       <c r="F11" s="2">
-        <v>108121.01</v>
+        <v>57747.42</v>
       </c>
       <c r="G11" s="4">
         <v>9.75</v>
       </c>
       <c r="H11" s="2">
-        <v>1536.77</v>
+        <v>821.27</v>
       </c>
       <c r="I11" s="2">
-        <v>14983.48</v>
+        <v>8007.35</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1172,25 +1172,25 @@
         <v>30</v>
       </c>
       <c r="C12" s="1">
-        <v>44585</v>
+        <v>44624</v>
       </c>
       <c r="D12" s="2">
-        <v>24638</v>
+        <v>39420</v>
       </c>
       <c r="E12" s="3">
-        <v>4.688</v>
+        <v>4.581</v>
       </c>
       <c r="F12" s="2">
-        <v>57747.42</v>
+        <v>90288</v>
       </c>
       <c r="G12" s="4">
         <v>10.75</v>
       </c>
       <c r="H12" s="2">
-        <v>821.27</v>
+        <v>1314</v>
       </c>
       <c r="I12" s="2">
-        <v>8828.62</v>
+        <v>14125.5</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1201,25 +1201,25 @@
         <v>32</v>
       </c>
       <c r="C13" s="1">
-        <v>44624</v>
+        <v>44626</v>
       </c>
       <c r="D13" s="2">
-        <v>39420</v>
+        <v>56093</v>
       </c>
       <c r="E13" s="3">
-        <v>4.581</v>
+        <v>4.575</v>
       </c>
       <c r="F13" s="2">
-        <v>90288</v>
+        <v>128322.34</v>
       </c>
       <c r="G13" s="4">
-        <v>15.75</v>
+        <v>8.75</v>
       </c>
       <c r="H13" s="2">
-        <v>1314</v>
+        <v>1869.77</v>
       </c>
       <c r="I13" s="2">
-        <v>20695.5</v>
+        <v>16360.46</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1230,25 +1230,25 @@
         <v>34</v>
       </c>
       <c r="C14" s="1">
-        <v>44626</v>
+        <v>44652</v>
       </c>
       <c r="D14" s="2">
-        <v>56093</v>
+        <v>7425</v>
       </c>
       <c r="E14" s="3">
-        <v>4.575</v>
+        <v>4.504</v>
       </c>
       <c r="F14" s="2">
-        <v>128322.34</v>
+        <v>16721.51</v>
       </c>
       <c r="G14" s="4">
-        <v>7.75</v>
+        <v>5.75</v>
       </c>
       <c r="H14" s="2">
-        <v>1869.77</v>
+        <v>247.5</v>
       </c>
       <c r="I14" s="2">
-        <v>14490.69</v>
+        <v>1423.13</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1259,25 +1259,25 @@
         <v>36</v>
       </c>
       <c r="C15" s="1">
-        <v>44652</v>
+        <v>44658</v>
       </c>
       <c r="D15" s="2">
-        <v>7425</v>
+        <v>9653</v>
       </c>
       <c r="E15" s="3">
-        <v>4.504</v>
+        <v>4.488</v>
       </c>
       <c r="F15" s="2">
-        <v>16721.51</v>
+        <v>21659.75</v>
       </c>
       <c r="G15" s="4">
-        <v>12.75</v>
+        <v>10.75</v>
       </c>
       <c r="H15" s="2">
-        <v>247.5</v>
+        <v>321.77</v>
       </c>
       <c r="I15" s="2">
-        <v>3155.63</v>
+        <v>3458.99</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1288,25 +1288,25 @@
         <v>38</v>
       </c>
       <c r="C16" s="1">
-        <v>44658</v>
+        <v>44700</v>
       </c>
       <c r="D16" s="2">
-        <v>9653</v>
+        <v>35843</v>
       </c>
       <c r="E16" s="3">
-        <v>4.488</v>
+        <v>4.373</v>
       </c>
       <c r="F16" s="2">
-        <v>21659.75</v>
+        <v>78363.6</v>
       </c>
       <c r="G16" s="4">
-        <v>6.75</v>
+        <v>11.75</v>
       </c>
       <c r="H16" s="2">
-        <v>321.77</v>
+        <v>1194.77</v>
       </c>
       <c r="I16" s="2">
-        <v>2171.93</v>
+        <v>14038.51</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1317,25 +1317,25 @@
         <v>40</v>
       </c>
       <c r="C17" s="1">
-        <v>44700</v>
+        <v>44733</v>
       </c>
       <c r="D17" s="2">
-        <v>35843</v>
+        <v>25650</v>
       </c>
       <c r="E17" s="3">
-        <v>4.373</v>
+        <v>4.282</v>
       </c>
       <c r="F17" s="2">
-        <v>78363.6</v>
+        <v>54919.11</v>
       </c>
       <c r="G17" s="4">
-        <v>10.75</v>
+        <v>3.75</v>
       </c>
       <c r="H17" s="2">
-        <v>1194.77</v>
+        <v>855</v>
       </c>
       <c r="I17" s="2">
-        <v>12843.74</v>
+        <v>3206.25</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1346,25 +1346,25 @@
         <v>42</v>
       </c>
       <c r="C18" s="1">
-        <v>44733</v>
+        <v>44738</v>
       </c>
       <c r="D18" s="2">
-        <v>25650</v>
+        <v>22208</v>
       </c>
       <c r="E18" s="3">
-        <v>4.282</v>
+        <v>4.268</v>
       </c>
       <c r="F18" s="2">
-        <v>54919.11</v>
+        <v>47397.35</v>
       </c>
       <c r="G18" s="4">
-        <v>5.75</v>
+        <v>15.75</v>
       </c>
       <c r="H18" s="2">
-        <v>855</v>
+        <v>740.27</v>
       </c>
       <c r="I18" s="2">
-        <v>4916.25</v>
+        <v>11659.2</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1375,25 +1375,25 @@
         <v>44</v>
       </c>
       <c r="C19" s="1">
-        <v>44738</v>
+        <v>44750</v>
       </c>
       <c r="D19" s="2">
-        <v>22208</v>
+        <v>92340</v>
       </c>
       <c r="E19" s="3">
-        <v>4.268</v>
+        <v>4.236</v>
       </c>
       <c r="F19" s="2">
-        <v>47397.35</v>
+        <v>195558.41</v>
       </c>
       <c r="G19" s="4">
-        <v>20.75</v>
+        <v>11.75</v>
       </c>
       <c r="H19" s="2">
-        <v>740.27</v>
+        <v>3078</v>
       </c>
       <c r="I19" s="2">
-        <v>15360.53</v>
+        <v>36166.5</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1404,25 +1404,25 @@
         <v>46</v>
       </c>
       <c r="C20" s="1">
-        <v>44750</v>
+        <v>44805</v>
       </c>
       <c r="D20" s="2">
-        <v>92340</v>
+        <v>10598</v>
       </c>
       <c r="E20" s="3">
-        <v>4.236</v>
+        <v>4.085</v>
       </c>
       <c r="F20" s="2">
-        <v>195558.41</v>
+        <v>21646.05</v>
       </c>
       <c r="G20" s="4">
-        <v>5.75</v>
+        <v>11.75</v>
       </c>
       <c r="H20" s="2">
-        <v>3078</v>
+        <v>353.27</v>
       </c>
       <c r="I20" s="2">
-        <v>17698.5</v>
+        <v>4150.88</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1433,25 +1433,25 @@
         <v>48</v>
       </c>
       <c r="C21" s="1">
-        <v>44805</v>
+        <v>44825</v>
       </c>
       <c r="D21" s="2">
-        <v>10598</v>
+        <v>64395</v>
       </c>
       <c r="E21" s="3">
-        <v>4.085</v>
+        <v>4.03</v>
       </c>
       <c r="F21" s="2">
-        <v>21646.05</v>
+        <v>129760.34</v>
       </c>
       <c r="G21" s="4">
-        <v>3.75</v>
+        <v>7.75</v>
       </c>
       <c r="H21" s="2">
-        <v>353.27</v>
+        <v>2146.5</v>
       </c>
       <c r="I21" s="2">
-        <v>1324.75</v>
+        <v>16635.38</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1462,25 +1462,25 @@
         <v>50</v>
       </c>
       <c r="C22" s="1">
-        <v>44825</v>
+        <v>44906</v>
       </c>
       <c r="D22" s="2">
-        <v>64395</v>
+        <v>21668</v>
       </c>
       <c r="E22" s="3">
-        <v>4.03</v>
+        <v>3.808</v>
       </c>
       <c r="F22" s="2">
-        <v>129760.34</v>
+        <v>41258.25</v>
       </c>
       <c r="G22" s="4">
-        <v>11.75</v>
+        <v>18.75</v>
       </c>
       <c r="H22" s="2">
-        <v>2146.5</v>
+        <v>722.27</v>
       </c>
       <c r="I22" s="2">
-        <v>25221.38</v>
+        <v>13542.5</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1491,25 +1491,25 @@
         <v>52</v>
       </c>
       <c r="C23" s="1">
-        <v>44906</v>
+        <v>44928</v>
       </c>
       <c r="D23" s="2">
-        <v>21668</v>
+        <v>7830</v>
       </c>
       <c r="E23" s="3">
-        <v>3.808</v>
+        <v>3.748</v>
       </c>
       <c r="F23" s="2">
-        <v>41258.25</v>
+        <v>14673.21</v>
       </c>
       <c r="G23" s="4">
-        <v>3.75</v>
+        <v>7.75</v>
       </c>
       <c r="H23" s="2">
-        <v>722.27</v>
+        <v>261</v>
       </c>
       <c r="I23" s="2">
-        <v>2708.5</v>
+        <v>2022.75</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1520,25 +1520,25 @@
         <v>54</v>
       </c>
       <c r="C24" s="1">
-        <v>44928</v>
+        <v>44972</v>
       </c>
       <c r="D24" s="2">
-        <v>7830</v>
+        <v>16538</v>
       </c>
       <c r="E24" s="3">
-        <v>3.748</v>
+        <v>3.627</v>
       </c>
       <c r="F24" s="2">
-        <v>14673.21</v>
+        <v>29994.95</v>
       </c>
       <c r="G24" s="4">
-        <v>13.75</v>
+        <v>3.75</v>
       </c>
       <c r="H24" s="2">
-        <v>261</v>
+        <v>551.27</v>
       </c>
       <c r="I24" s="2">
-        <v>3588.75</v>
+        <v>2067.25</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1549,25 +1549,25 @@
         <v>56</v>
       </c>
       <c r="C25" s="1">
-        <v>44972</v>
+        <v>44978</v>
       </c>
       <c r="D25" s="2">
-        <v>16538</v>
+        <v>17483</v>
       </c>
       <c r="E25" s="3">
-        <v>3.627</v>
+        <v>3.611</v>
       </c>
       <c r="F25" s="2">
-        <v>29994.95</v>
+        <v>31565.2</v>
       </c>
       <c r="G25" s="4">
-        <v>3.75</v>
+        <v>7.75</v>
       </c>
       <c r="H25" s="2">
-        <v>551.27</v>
+        <v>582.77</v>
       </c>
       <c r="I25" s="2">
-        <v>2067.25</v>
+        <v>4516.44</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1578,518 +1578,518 @@
         <v>58</v>
       </c>
       <c r="C26" s="1">
-        <v>44978</v>
+        <v>45005</v>
       </c>
       <c r="D26" s="2">
-        <v>17483</v>
+        <v>37395</v>
       </c>
       <c r="E26" s="3">
-        <v>3.611</v>
+        <v>3.537</v>
       </c>
       <c r="F26" s="2">
-        <v>31565.2</v>
+        <v>66132.8</v>
       </c>
       <c r="G26" s="4">
         <v>9.75</v>
       </c>
       <c r="H26" s="2">
-        <v>582.77</v>
+        <v>1246.5</v>
       </c>
       <c r="I26" s="2">
-        <v>5681.98</v>
+        <v>12153.38</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C27" s="1">
-        <v>45005</v>
+        <v>45030</v>
       </c>
       <c r="D27" s="2">
-        <v>37395</v>
+        <v>13298</v>
       </c>
       <c r="E27" s="3">
-        <v>3.537</v>
+        <v>3.468</v>
       </c>
       <c r="F27" s="2">
-        <v>66132.8</v>
+        <v>23062.01</v>
       </c>
       <c r="G27" s="4">
-        <v>7.75</v>
+        <v>12.75</v>
       </c>
       <c r="H27" s="2">
-        <v>1246.5</v>
+        <v>443.27</v>
       </c>
       <c r="I27" s="2">
-        <v>9660.38</v>
+        <v>5651.65</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C28" s="1">
-        <v>45030</v>
+        <v>45046</v>
       </c>
       <c r="D28" s="2">
-        <v>13298</v>
+        <v>22815</v>
       </c>
       <c r="E28" s="3">
-        <v>3.468</v>
+        <v>3.425</v>
       </c>
       <c r="F28" s="2">
-        <v>23062.01</v>
+        <v>39066.78</v>
       </c>
       <c r="G28" s="4">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
       <c r="H28" s="2">
-        <v>443.27</v>
+        <v>760.5</v>
       </c>
       <c r="I28" s="2">
-        <v>2992.05</v>
+        <v>4372.88</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C29" s="1">
-        <v>45046</v>
+        <v>45129</v>
       </c>
       <c r="D29" s="2">
-        <v>22815</v>
+        <v>8235</v>
       </c>
       <c r="E29" s="3">
-        <v>3.425</v>
+        <v>3.197</v>
       </c>
       <c r="F29" s="2">
-        <v>39066.78</v>
+        <v>13164.72</v>
       </c>
       <c r="G29" s="4">
-        <v>9.75</v>
+        <v>6.75</v>
       </c>
       <c r="H29" s="2">
-        <v>760.5</v>
+        <v>274.5</v>
       </c>
       <c r="I29" s="2">
-        <v>7414.88</v>
+        <v>1852.88</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C30" s="1">
-        <v>45129</v>
+        <v>45131</v>
       </c>
       <c r="D30" s="2">
-        <v>8235</v>
+        <v>17078</v>
       </c>
       <c r="E30" s="3">
-        <v>3.197</v>
+        <v>3.192</v>
       </c>
       <c r="F30" s="2">
-        <v>13164.72</v>
+        <v>27254.62</v>
       </c>
       <c r="G30" s="4">
-        <v>19.75</v>
+        <v>6.75</v>
       </c>
       <c r="H30" s="2">
-        <v>274.5</v>
+        <v>569.27</v>
       </c>
       <c r="I30" s="2">
-        <v>5421.38</v>
+        <v>3842.55</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C31" s="1">
-        <v>45131</v>
+        <v>45140</v>
       </c>
       <c r="D31" s="2">
-        <v>17078</v>
+        <v>10733</v>
       </c>
       <c r="E31" s="3">
-        <v>3.192</v>
+        <v>3.167</v>
       </c>
       <c r="F31" s="2">
-        <v>27254.62</v>
+        <v>16996.37</v>
       </c>
       <c r="G31" s="4">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="H31" s="2">
-        <v>569.27</v>
+        <v>357.77</v>
       </c>
       <c r="I31" s="2">
-        <v>2704.02</v>
+        <v>1341.63</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C32" s="1">
-        <v>45140</v>
+        <v>45163</v>
       </c>
       <c r="D32" s="2">
-        <v>10733</v>
+        <v>41850</v>
       </c>
       <c r="E32" s="3">
-        <v>3.167</v>
+        <v>3.104</v>
       </c>
       <c r="F32" s="2">
-        <v>16996.37</v>
+        <v>64953.49</v>
       </c>
       <c r="G32" s="4">
-        <v>15.75</v>
+        <v>18.75</v>
       </c>
       <c r="H32" s="2">
-        <v>357.77</v>
+        <v>1395</v>
       </c>
       <c r="I32" s="2">
-        <v>5634.83</v>
+        <v>26156.25</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="1">
-        <v>45163</v>
+        <v>45174</v>
       </c>
       <c r="D33" s="2">
-        <v>41850</v>
+        <v>11003</v>
       </c>
       <c r="E33" s="3">
-        <v>3.104</v>
+        <v>3.074</v>
       </c>
       <c r="F33" s="2">
-        <v>64953.49</v>
+        <v>16911.46</v>
       </c>
       <c r="G33" s="4">
-        <v>3.75</v>
+        <v>8.75</v>
       </c>
       <c r="H33" s="2">
-        <v>1395</v>
+        <v>366.77</v>
       </c>
       <c r="I33" s="2">
-        <v>5231.25</v>
+        <v>3209.21</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C34" s="1">
-        <v>45174</v>
+        <v>45207</v>
       </c>
       <c r="D34" s="2">
-        <v>11003</v>
+        <v>25313</v>
       </c>
       <c r="E34" s="3">
-        <v>3.074</v>
+        <v>2.984</v>
       </c>
       <c r="F34" s="2">
-        <v>16911.46</v>
+        <v>37761.45</v>
       </c>
       <c r="G34" s="4">
-        <v>3.75</v>
+        <v>8.75</v>
       </c>
       <c r="H34" s="2">
-        <v>366.77</v>
+        <v>843.77</v>
       </c>
       <c r="I34" s="2">
-        <v>1375.38</v>
+        <v>7382.96</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C35" s="1">
-        <v>45207</v>
+        <v>45216</v>
       </c>
       <c r="D35" s="2">
-        <v>25313</v>
+        <v>10598</v>
       </c>
       <c r="E35" s="3">
-        <v>2.984</v>
+        <v>2.959</v>
       </c>
       <c r="F35" s="2">
-        <v>37761.45</v>
+        <v>15679.23</v>
       </c>
       <c r="G35" s="4">
-        <v>10.75</v>
+        <v>3.75</v>
       </c>
       <c r="H35" s="2">
-        <v>843.77</v>
+        <v>353.27</v>
       </c>
       <c r="I35" s="2">
-        <v>9070.49</v>
+        <v>1324.75</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C36" s="1">
-        <v>45216</v>
+        <v>45233</v>
       </c>
       <c r="D36" s="2">
-        <v>10598</v>
+        <v>17280</v>
       </c>
       <c r="E36" s="3">
-        <v>2.959</v>
+        <v>2.912</v>
       </c>
       <c r="F36" s="2">
-        <v>15679.23</v>
+        <v>25162.52</v>
       </c>
       <c r="G36" s="4">
-        <v>16.75</v>
+        <v>18.75</v>
       </c>
       <c r="H36" s="2">
-        <v>353.27</v>
+        <v>576</v>
       </c>
       <c r="I36" s="2">
-        <v>5917.22</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C37" s="1">
-        <v>45233</v>
+        <v>45241</v>
       </c>
       <c r="D37" s="2">
-        <v>17280</v>
+        <v>11070</v>
       </c>
       <c r="E37" s="3">
-        <v>2.912</v>
+        <v>2.89</v>
       </c>
       <c r="F37" s="2">
-        <v>25162.52</v>
+        <v>15998.42</v>
       </c>
       <c r="G37" s="4">
         <v>10.75</v>
       </c>
       <c r="H37" s="2">
-        <v>576</v>
+        <v>369</v>
       </c>
       <c r="I37" s="2">
-        <v>6192</v>
+        <v>3966.75</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C38" s="1">
-        <v>45241</v>
+        <v>45275</v>
       </c>
       <c r="D38" s="2">
-        <v>11070</v>
+        <v>38610</v>
       </c>
       <c r="E38" s="3">
-        <v>2.89</v>
+        <v>2.797</v>
       </c>
       <c r="F38" s="2">
-        <v>15998.42</v>
+        <v>54001.11</v>
       </c>
       <c r="G38" s="4">
-        <v>15.75</v>
+        <v>11.75</v>
       </c>
       <c r="H38" s="2">
-        <v>369</v>
+        <v>1287</v>
       </c>
       <c r="I38" s="2">
-        <v>5811.75</v>
+        <v>15122.25</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C39" s="1">
-        <v>45275</v>
+        <v>45330</v>
       </c>
       <c r="D39" s="2">
-        <v>38610</v>
+        <v>19575</v>
       </c>
       <c r="E39" s="3">
-        <v>2.797</v>
+        <v>2.647</v>
       </c>
       <c r="F39" s="2">
-        <v>54001.11</v>
+        <v>25903.36</v>
       </c>
       <c r="G39" s="4">
-        <v>8.75</v>
+        <v>7.75</v>
       </c>
       <c r="H39" s="2">
-        <v>1287</v>
+        <v>652.5</v>
       </c>
       <c r="I39" s="2">
-        <v>11261.25</v>
+        <v>5056.88</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C40" s="1">
-        <v>45330</v>
+        <v>45335</v>
       </c>
       <c r="D40" s="2">
-        <v>19575</v>
+        <v>15930</v>
       </c>
       <c r="E40" s="3">
-        <v>2.647</v>
+        <v>2.633</v>
       </c>
       <c r="F40" s="2">
-        <v>25903.36</v>
+        <v>20970.86</v>
       </c>
       <c r="G40" s="4">
-        <v>14.75</v>
+        <v>20.75</v>
       </c>
       <c r="H40" s="2">
-        <v>652.5</v>
+        <v>531</v>
       </c>
       <c r="I40" s="2">
-        <v>9624.38</v>
+        <v>11018.25</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C41" s="1">
-        <v>45335</v>
+        <v>45343</v>
       </c>
       <c r="D41" s="2">
-        <v>15930</v>
+        <v>11745</v>
       </c>
       <c r="E41" s="3">
-        <v>2.633</v>
+        <v>2.611</v>
       </c>
       <c r="F41" s="2">
-        <v>20970.86</v>
+        <v>15332.86</v>
       </c>
       <c r="G41" s="4">
-        <v>11.75</v>
+        <v>8.75</v>
       </c>
       <c r="H41" s="2">
-        <v>531</v>
+        <v>391.5</v>
       </c>
       <c r="I41" s="2">
-        <v>6239.25</v>
+        <v>3425.63</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C42" s="1">
-        <v>45343</v>
+        <v>45379</v>
       </c>
       <c r="D42" s="2">
-        <v>11745</v>
+        <v>38678</v>
       </c>
       <c r="E42" s="3">
-        <v>2.611</v>
+        <v>2.512</v>
       </c>
       <c r="F42" s="2">
-        <v>15332.86</v>
+        <v>48585.93</v>
       </c>
       <c r="G42" s="4">
-        <v>14.75</v>
+        <v>7.75</v>
       </c>
       <c r="H42" s="2">
-        <v>391.5</v>
+        <v>1289.27</v>
       </c>
       <c r="I42" s="2">
-        <v>5774.63</v>
+        <v>9991.82</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
         <v>91</v>
       </c>
       <c r="C43" s="1">
-        <v>45379</v>
+        <v>45426</v>
       </c>
       <c r="D43" s="2">
-        <v>38678</v>
+        <v>24233</v>
       </c>
       <c r="E43" s="3">
-        <v>2.512</v>
+        <v>2.384</v>
       </c>
       <c r="F43" s="2">
-        <v>48585.93</v>
+        <v>28880.42</v>
       </c>
       <c r="G43" s="4">
-        <v>3.75</v>
+        <v>8.75</v>
       </c>
       <c r="H43" s="2">
-        <v>1289.27</v>
+        <v>807.77</v>
       </c>
       <c r="I43" s="2">
-        <v>4834.75</v>
+        <v>7067.96</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2100,25 +2100,25 @@
         <v>93</v>
       </c>
       <c r="C44" s="1">
-        <v>45426</v>
+        <v>45477</v>
       </c>
       <c r="D44" s="2">
-        <v>24233</v>
+        <v>10328</v>
       </c>
       <c r="E44" s="3">
-        <v>2.384</v>
+        <v>2.244</v>
       </c>
       <c r="F44" s="2">
-        <v>28880.42</v>
+        <v>11587.17</v>
       </c>
       <c r="G44" s="4">
-        <v>11.75</v>
+        <v>12.75</v>
       </c>
       <c r="H44" s="2">
-        <v>807.77</v>
+        <v>344.27</v>
       </c>
       <c r="I44" s="2">
-        <v>9491.26</v>
+        <v>4389.4</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2129,25 +2129,25 @@
         <v>95</v>
       </c>
       <c r="C45" s="1">
-        <v>45477</v>
+        <v>45511</v>
       </c>
       <c r="D45" s="2">
-        <v>10328</v>
+        <v>18428</v>
       </c>
       <c r="E45" s="3">
-        <v>2.244</v>
+        <v>2.151</v>
       </c>
       <c r="F45" s="2">
-        <v>11587.17</v>
+        <v>19816.41</v>
       </c>
       <c r="G45" s="4">
         <v>3.75</v>
       </c>
       <c r="H45" s="2">
-        <v>344.27</v>
+        <v>614.27</v>
       </c>
       <c r="I45" s="2">
-        <v>1291</v>
+        <v>2303.5</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -2158,25 +2158,25 @@
         <v>97</v>
       </c>
       <c r="C46" s="1">
-        <v>45511</v>
+        <v>45525</v>
       </c>
       <c r="D46" s="2">
-        <v>18428</v>
+        <v>20318</v>
       </c>
       <c r="E46" s="3">
-        <v>2.151</v>
+        <v>2.112</v>
       </c>
       <c r="F46" s="2">
-        <v>19816.41</v>
+        <v>21459.15</v>
       </c>
       <c r="G46" s="4">
-        <v>3.75</v>
+        <v>-3.25</v>
       </c>
       <c r="H46" s="2">
-        <v>614.27</v>
+        <v>677.27</v>
       </c>
       <c r="I46" s="2">
-        <v>2303.5</v>
+        <v>-2201.12</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -2199,13 +2199,13 @@
         <v>13667.88</v>
       </c>
       <c r="G47" s="4">
-        <v>7.75</v>
+        <v>3.75</v>
       </c>
       <c r="H47" s="2">
         <v>438.77</v>
       </c>
       <c r="I47" s="2">
-        <v>3400.44</v>
+        <v>1645.38</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2228,13 +2228,13 @@
         <v>14815.82</v>
       </c>
       <c r="G48" s="4">
-        <v>-3.25</v>
+        <v>14.75</v>
       </c>
       <c r="H48" s="2">
         <v>497.27</v>
       </c>
       <c r="I48" s="2">
-        <v>-1616.12</v>
+        <v>7334.68</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -2257,13 +2257,13 @@
         <v>8438.79</v>
       </c>
       <c r="G49" s="4">
-        <v>5.75</v>
+        <v>18.75</v>
       </c>
       <c r="H49" s="2">
         <v>288</v>
       </c>
       <c r="I49" s="2">
-        <v>1656</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2286,13 +2286,13 @@
         <v>9736.64</v>
       </c>
       <c r="G50" s="4">
-        <v>11.75</v>
+        <v>8.75</v>
       </c>
       <c r="H50" s="2">
         <v>337.5</v>
       </c>
       <c r="I50" s="2">
-        <v>3965.63</v>
+        <v>2953.13</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2315,13 +2315,13 @@
         <v>19214.07</v>
       </c>
       <c r="G51" s="4">
-        <v>9.75</v>
+        <v>13.75</v>
       </c>
       <c r="H51" s="2">
         <v>749.27</v>
       </c>
       <c r="I51" s="2">
-        <v>7305.35</v>
+        <v>10302.42</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2335,22 +2335,22 @@
         <v>45718</v>
       </c>
       <c r="D52" s="2">
-        <v>17010</v>
+        <v>21195</v>
       </c>
       <c r="E52" s="3">
         <v>1.584</v>
       </c>
       <c r="F52" s="2">
-        <v>13468.19</v>
+        <v>16781.79</v>
       </c>
       <c r="G52" s="4">
-        <v>12.75</v>
+        <v>15.5</v>
       </c>
       <c r="H52" s="2">
-        <v>567</v>
+        <v>706.5</v>
       </c>
       <c r="I52" s="2">
-        <v>7229.25</v>
+        <v>10950.75</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -2373,13 +2373,13 @@
         <v>13206.26</v>
       </c>
       <c r="G53" s="4">
-        <v>17.75</v>
+        <v>7.75</v>
       </c>
       <c r="H53" s="2">
         <v>564.77</v>
       </c>
       <c r="I53" s="2">
-        <v>10024.61</v>
+        <v>4376.94</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -2402,13 +2402,13 @@
         <v>10223.47</v>
       </c>
       <c r="G54" s="4">
-        <v>5.75</v>
+        <v>19.75</v>
       </c>
       <c r="H54" s="2">
         <v>470.27</v>
       </c>
       <c r="I54" s="2">
-        <v>2704.03</v>
+        <v>9287.77</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -2431,13 +2431,13 @@
         <v>11994.72</v>
       </c>
       <c r="G55" s="4">
-        <v>14.75</v>
+        <v>16.75</v>
       </c>
       <c r="H55" s="2">
         <v>587.27</v>
       </c>
       <c r="I55" s="2">
-        <v>8662.18</v>
+        <v>9836.72</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2460,13 +2460,13 @@
         <v>9009.68</v>
       </c>
       <c r="G56" s="4">
-        <v>20.75</v>
+        <v>15.75</v>
       </c>
       <c r="H56" s="2">
         <v>463.5</v>
       </c>
       <c r="I56" s="2">
-        <v>9617.63</v>
+        <v>7300.13</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -2489,13 +2489,13 @@
         <v>16402.26</v>
       </c>
       <c r="G57" s="4">
-        <v>19.75</v>
+        <v>6.75</v>
       </c>
       <c r="H57" s="2">
         <v>875.27</v>
       </c>
       <c r="I57" s="2">
-        <v>17286.52</v>
+        <v>5908.05</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2518,13 +2518,13 @@
         <v>10562.55</v>
       </c>
       <c r="G58" s="4">
-        <v>10.75</v>
+        <v>4.75</v>
       </c>
       <c r="H58" s="2">
         <v>589.5</v>
       </c>
       <c r="I58" s="2">
-        <v>6337.13</v>
+        <v>2800.13</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -2576,13 +2576,13 @@
         <v>9808.77</v>
       </c>
       <c r="G60" s="4">
-        <v>14.75</v>
+        <v>5.75</v>
       </c>
       <c r="H60" s="2">
         <v>702</v>
       </c>
       <c r="I60" s="2">
-        <v>10354.5</v>
+        <v>4036.5</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -2605,13 +2605,13 @@
         <v>5371.82</v>
       </c>
       <c r="G61" s="4">
-        <v>9.75</v>
+        <v>13.75</v>
       </c>
       <c r="H61" s="2">
         <v>434.27</v>
       </c>
       <c r="I61" s="2">
-        <v>4234.1</v>
+        <v>5971.17</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2634,13 +2634,13 @@
         <v>4481.19</v>
       </c>
       <c r="G62" s="4">
-        <v>8.75</v>
+        <v>14.75</v>
       </c>
       <c r="H62" s="2">
         <v>362.27</v>
       </c>
       <c r="I62" s="2">
-        <v>3169.83</v>
+        <v>5343.43</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2663,13 +2663,13 @@
         <v>4741.83</v>
       </c>
       <c r="G63" s="4">
-        <v>11.75</v>
+        <v>15.75</v>
       </c>
       <c r="H63" s="2">
         <v>445.5</v>
       </c>
       <c r="I63" s="2">
-        <v>5234.63</v>
+        <v>7016.63</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2692,13 +2692,13 @@
         <v>4633.64</v>
       </c>
       <c r="G64" s="4">
-        <v>9.75</v>
+        <v>4.75</v>
       </c>
       <c r="H64" s="2">
         <v>486</v>
       </c>
       <c r="I64" s="2">
-        <v>4738.5</v>
+        <v>2308.5</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -2712,22 +2712,22 @@
         <v>46153</v>
       </c>
       <c r="D65" s="2">
-        <v>20318</v>
+        <v>17010</v>
       </c>
       <c r="E65" s="3">
         <v>0.392</v>
       </c>
       <c r="F65" s="2">
-        <v>3980.1</v>
+        <v>3332.1</v>
       </c>
       <c r="G65" s="4">
-        <v>6.75</v>
+        <v>4.75</v>
       </c>
       <c r="H65" s="2">
-        <v>677.27</v>
+        <v>567</v>
       </c>
       <c r="I65" s="2">
-        <v>4571.55</v>
+        <v>2693.25</v>
       </c>
     </row>
     <row r="66" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="E66" s="13"/>
       <c r="F66" s="12">
-        <v>2432559.68</v>
+        <v>2404219.55</v>
       </c>
       <c r="G66" s="14"/>
       <c r="H66" s="12"/>
       <c r="I66" s="12">
-        <v>494221.72</v>
+        <v>511850.89</v>
       </c>
     </row>
   </sheetData>
